--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilherme\OneDrive - SPARK ELETRONICA LTDA\Área de Trabalho\Automacao-assinatura-de-emaill\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Linkedin\Automacao-Assinaturas-de-Email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92A3362-621C-4DB2-A367-36E39016A87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A128C3-CEF9-4F19-942C-C238B623F1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="4185" windowWidth="28800" windowHeight="11415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>NOME</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>RAMAL</t>
+  </si>
+  <si>
+    <t>Guilherme Araujo</t>
+  </si>
+  <si>
+    <t>Analista de Sistemas</t>
   </si>
 </sst>
 </file>
@@ -351,15 +357,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -368,6 +374,17 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
